--- a/Employee_Reports_wi52/Trevin Christopher Neydorf Q0531.xlsx
+++ b/Employee_Reports_wi52/Trevin Christopher Neydorf Q0531.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -593,53 +593,53 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>EWS EQ  (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-004</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2024</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>04-Oct-2026</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -887,102 +887,102 @@
       <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>TT+RA (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-007</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2024</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2026</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>CS-Hoist (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-001</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>27-Aug-2024</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>27-Aug-2026</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1657,11 +1657,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1706,11 +1706,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1734,20 +1734,20 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>22-Aug-2028</t>
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>315</v>
+        <v>725</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
